--- a/data/trans_dic/IP31KM02_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>63,98%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,46; 68,79</t>
+          <t>57,2; 73,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52,89; 71,08</t>
+          <t>53,7; 69,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55,38; 67,92</t>
+          <t>58,11; 69,01</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>59,17%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>48,32; 65,51</t>
+          <t>50,04; 68,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,16; 67,04</t>
+          <t>49,32; 66,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51,67; 63,62</t>
+          <t>52,74; 65,39</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>61,51%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50,34; 74,95</t>
+          <t>49,25; 71,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,49; 68,98</t>
+          <t>48,54; 74,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51,26; 68,67</t>
+          <t>52,51; 69,29</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,48; 53,39</t>
+          <t>47,56; 61,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,95; 60,28</t>
+          <t>44,33; 56,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,23; 54,2</t>
+          <t>48,24; 58,32</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>55,35; 70,99</t>
+          <t>48,49; 68,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,62; 68,11</t>
+          <t>54,82; 70,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,02; 66,51</t>
+          <t>53,46; 67,11</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>64,1%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55,09; 74,21</t>
+          <t>49,46; 70,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,46; 68,77</t>
+          <t>58,06; 76,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,01; 69,44</t>
+          <t>56,37; 71,03</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47,58; 59,89</t>
+          <t>55,84; 63,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>54,26; 61,87</t>
+          <t>55,51; 62,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52,93; 60,0</t>
+          <t>57,03; 62,06</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>96</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>61373</t>
+          <t>79610</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84953</t>
+          <t>62136</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146327</t>
+          <t>141746</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>52335; 69967</t>
+          <t>69326; 88657</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>71491; 96085</t>
+          <t>53887; 70222</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>131178; 160890</t>
+          <t>128742; 152899</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>53746</t>
+          <t>53771</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>54538</t>
+          <t>55867</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108285</t>
+          <t>109638</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>45125; 61178</t>
+          <t>44978; 61787</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45127; 62826</t>
+          <t>47053; 63431</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96677; 119030</t>
+          <t>97721; 121169</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31782</t>
+          <t>33777</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36130</t>
+          <t>32559</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67911</t>
+          <t>66336</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25213; 37544</t>
+          <t>27506; 39985</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28979; 43000</t>
+          <t>25244; 38857</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57629; 77198</t>
+          <t>56629; 74729</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>141</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>94900</t>
+          <t>109041</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>114476</t>
+          <t>89693</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>209376</t>
+          <t>198734</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63541; 115068</t>
+          <t>93845; 122133</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97707; 128180</t>
+          <t>78298; 100606</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>163713; 232073</t>
+          <t>180390; 218093</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>106</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72695</t>
+          <t>88200</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>95790</t>
+          <t>72850</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168486</t>
+          <t>161050</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>63940; 82003</t>
+          <t>70588; 100405</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>72741; 108612</t>
+          <t>63302; 81012</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>143036; 182892</t>
+          <t>139558; 175183</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>63</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>44995</t>
+          <t>39493</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>40286</t>
+          <t>47826</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85280</t>
+          <t>87319</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>37956; 51130</t>
+          <t>32579; 46713</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>32068; 47473</t>
+          <t>40846; 53693</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74498; 95780</t>
+          <t>76786; 96759</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>533</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>556</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>359490</t>
+          <t>403891</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>426174</t>
+          <t>360931</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>785664</t>
+          <t>764823</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>306944; 386359</t>
+          <t>377292; 428499</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>397381; 453081</t>
+          <t>338730; 379008</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>729070; 826440</t>
+          <t>733335; 798033</t>
         </is>
       </c>
     </row>
